--- a/Assessment Questions/CDA/PYF-110/PYTHON BASICS/Python Variables/Python Variables.xlsx
+++ b/Assessment Questions/CDA/PYF-110/PYTHON BASICS/Python Variables/Python Variables.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python Variables Questions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -422,6 +422,11 @@
           <t>Question</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -429,6 +434,11 @@
           <t>Create a variable to store your name and print it.</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -436,6 +446,11 @@
           <t>Assign two variables with numbers and print their sum.</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -443,6 +458,11 @@
           <t>Create variables of type int, float, and string, and print their types.</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -450,6 +470,11 @@
           <t>Swap values of two variables without using a third variable.</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -457,6 +482,11 @@
           <t>Assign multiple variables in one line and print them.</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -464,6 +494,11 @@
           <t>Take user input and store it in a variable, then print its type.</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -471,6 +506,11 @@
           <t>Convert a string variable to an integer and perform arithmetic.</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -478,6 +518,11 @@
           <t>Create a constant variable and try modifying it. Observe behavior.</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -485,6 +530,11 @@
           <t>Use global and local variables in a function and print both.</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -492,6 +542,11 @@
           <t>Assign a list to a variable and modify one element.</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -499,6 +554,11 @@
           <t>Demonstrate variable unpacking with a tuple.</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -506,6 +566,11 @@
           <t>Create a variable inside a loop and access it outside.</t>
         </is>
       </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -513,6 +578,11 @@
           <t>Demonstrate mutable vs immutable variable behavior.</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -520,6 +590,11 @@
           <t>Use variables to store a dictionary and update values dynamically.</t>
         </is>
       </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -527,6 +602,11 @@
           <t>Create a function that modifies a variable passed as argument.</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -534,6 +614,11 @@
           <t>Use *args to pass multiple values into a function.</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -541,6 +626,11 @@
           <t>Use **kwargs to store dynamic key-value pairs.</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -548,6 +638,11 @@
           <t>Demonstrate variable shadowing inside nested functions.</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -555,11 +650,21 @@
           <t>Use variables with lambda functions.</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
           <t>Create a class and use instance variables and class variables.</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Coding</t>
         </is>
       </c>
     </row>
